--- a/18_Insurance_Actuarial/_template_INSURANCE.xlsx
+++ b/18_Insurance_Actuarial/_template_INSURANCE.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
   <si>
     <t xml:space="preserve">[INSURER] — Insurance / Actuarial Model</t>
   </si>
@@ -37,10 +37,19 @@
     <t xml:space="preserve">P&amp;C / Life / Health / Reinsurance</t>
   </si>
   <si>
+    <t xml:space="preserve">Carrier / cedant:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[fill in]</t>
+  </si>
+  <si>
     <t xml:space="preserve">Last refreshed:</t>
   </si>
   <si>
     <t xml:space="preserve">[date]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next reserve review date:</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh cadence:</t>
@@ -711,7 +720,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C6"/>
+  <dimension ref="B2:C8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -747,6 +756,22 @@
       </c>
       <c r="C6" s="3" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -776,12 +801,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -789,7 +814,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -797,7 +822,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
@@ -805,7 +830,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
@@ -813,7 +838,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10" s="6" t="str">
         <f aca="false">IFERROR((C6+C7)/C5,"-")</f>
@@ -822,7 +847,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C11" s="6" t="str">
         <f aca="false">IFERROR(C8/C5,"-")</f>
@@ -831,14 +856,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C12" s="7" t="str">
         <f aca="false">IFERROR(C10+C11,"-")</f>
         <v>-</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -868,41 +893,41 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -933,7 +958,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -961,7 +986,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
@@ -986,7 +1011,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
@@ -1008,7 +1033,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>0</v>
@@ -1027,7 +1052,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
@@ -1043,7 +1068,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D14" s="12" t="str">
         <f aca="false">IFERROR(SUM(D5:D9)/SUM(C5:C9),"-")</f>
@@ -1068,7 +1093,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C15" s="12" t="str">
         <f aca="false">IFERROR(D14*D15,"-")</f>
@@ -1096,7 +1121,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I17" s="13" t="n">
         <f aca="false">SUM(I5:I10)</f>
@@ -1109,7 +1134,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1139,12 +1164,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -1152,7 +1177,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -1160,7 +1185,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
@@ -1168,7 +1193,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
@@ -1176,7 +1201,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">C5+C6-C7-C8</f>
@@ -1185,7 +1210,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>0</v>
@@ -1218,17 +1243,17 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -1236,7 +1261,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -1244,12 +1269,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">'Loss Reserve Triangle'!J17</f>
@@ -1258,7 +1283,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">IFERROR(C5+C10,"-")</f>
@@ -1267,26 +1292,26 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C12" s="6" t="str">
         <f aca="false">IFERROR(C10/C11,"-")</f>
         <v>-</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="15" t="str">
         <f aca="false">IFERROR(C11/C6,"-")</f>
         <v>-</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1316,17 +1341,17 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>0</v>
@@ -1334,7 +1359,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -1342,12 +1367,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10" s="14" t="str">
         <f aca="false">IFERROR('Underwriting Ratios'!C5*(1-'Underwriting Ratios'!C12),"-")</f>
@@ -1356,7 +1381,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C11" s="13" t="str">
         <f aca="false">IFERROR(C10+C5,"-")</f>
@@ -1365,14 +1390,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C12" s="7" t="str">
         <f aca="false">IFERROR(C11/C6,"-")</f>
         <v>-</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1403,24 +1428,24 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/18_Insurance_Actuarial/_template_INSURANCE.xlsx
+++ b/18_Insurance_Actuarial/_template_INSURANCE.xlsx
@@ -11,10 +11,11 @@
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Underwriting Ratios" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Loss Reserve Triangle" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Embedded Value" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Reserve Summary" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Profitability" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="RefreshLog" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Bornhuetter-Ferguson" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Embedded Value" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Reserve Summary" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Profitability" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="RefreshLog" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="86">
   <si>
     <t xml:space="preserve">[INSURER] — Insurance / Actuarial Model</t>
   </si>
@@ -143,6 +144,54 @@
   </si>
   <si>
     <t xml:space="preserve">Standard volume-weighted chain-ladder. Link factors use only accident years with data in both adjacent columns (upper-left triangle) — that's why each factor's denominator shrinks moving right.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bornhuetter-Ferguson Reserving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected loss ratio (a priori, %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From pricing / plan, independent of the loss triangle itself — the whole point is not to derive this from the same thin data chain-ladder relies on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accident Yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earned Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected Ultimate (ELR x Premium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual Reported (latest diagonal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Reported (1/CDF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BF IBNR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BF Ultimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chain-Ladder Ultimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BF - CL Difference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BF Ultimate = Actual reported + Expected ultimate x (1 - 1/CDF). At full maturity (CDF=1) the IBNR term vanishes and BF collapses to exactly the actual/chain-ladder figure — check the AY2020/AY2021 rows above, where CDF=1.000 and the BF-CL difference is exactly 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For the least mature year (highest CDF), chain-ladder leans hardest on the thinnest, noisiest actual data — that's exactly where BF's independent prior does the most work pulling the estimate away from a potentially unstable chain-ladder projection.</t>
   </si>
   <si>
     <t xml:space="preserve">Embedded Value (life/health simplified)</t>
@@ -399,72 +448,88 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -723,54 +788,54 @@
   <dimension ref="B2:C8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -793,76 +858,76 @@
   <dimension ref="B2:D12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="6" t="str">
+      <c r="C10" s="7" t="str">
         <f aca="false">IFERROR((C6+C7)/C5,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="6" t="str">
+      <c r="C11" s="7" t="str">
         <f aca="false">IFERROR(C8/C5,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="7" t="str">
+      <c r="C12" s="8" t="str">
         <f aca="false">IFERROR(C10+C11,"-")</f>
         <v>-</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>18</v>
       </c>
     </row>
@@ -885,255 +950,255 @@
   <dimension ref="B2:J18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="11" t="n">
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="12" t="n">
         <f aca="false">IFERROR(H5*H15,"-")</f>
         <v>0</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" s="12" t="n">
         <f aca="false">IFERROR(I5-H5,"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="11" t="str">
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="12" t="str">
         <f aca="false">IFERROR(G6*G15,"-")</f>
         <v>-</v>
       </c>
-      <c r="J6" s="11" t="str">
+      <c r="J6" s="12" t="str">
         <f aca="false">IFERROR(I6-G6,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="11" t="str">
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="12" t="str">
         <f aca="false">IFERROR(F7*F15,"-")</f>
         <v>-</v>
       </c>
-      <c r="J7" s="11" t="str">
+      <c r="J7" s="12" t="str">
         <f aca="false">IFERROR(I7-F7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="11" t="str">
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12" t="str">
         <f aca="false">IFERROR(E8*E15,"-")</f>
         <v>-</v>
       </c>
-      <c r="J8" s="11" t="str">
+      <c r="J8" s="12" t="str">
         <f aca="false">IFERROR(I8-E8,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="11" t="str">
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12" t="str">
         <f aca="false">IFERROR(D9*D15,"-")</f>
         <v>-</v>
       </c>
-      <c r="J9" s="11" t="str">
+      <c r="J9" s="12" t="str">
         <f aca="false">IFERROR(I9-D9,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="11" t="str">
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12" t="str">
         <f aca="false">IFERROR(C10*C15,"-")</f>
         <v>-</v>
       </c>
-      <c r="J10" s="11" t="str">
+      <c r="J10" s="12" t="str">
         <f aca="false">IFERROR(I10-C10,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="12" t="str">
+      <c r="D14" s="13" t="str">
         <f aca="false">IFERROR(SUM(D5:D9)/SUM(C5:C9),"-")</f>
         <v>-</v>
       </c>
-      <c r="E14" s="12" t="str">
+      <c r="E14" s="13" t="str">
         <f aca="false">IFERROR(SUM(E5:E8)/SUM(D5:D8),"-")</f>
         <v>-</v>
       </c>
-      <c r="F14" s="12" t="str">
+      <c r="F14" s="13" t="str">
         <f aca="false">IFERROR(SUM(F5:F7)/SUM(E5:E7),"-")</f>
         <v>-</v>
       </c>
-      <c r="G14" s="12" t="str">
+      <c r="G14" s="13" t="str">
         <f aca="false">IFERROR(SUM(G5:G6)/SUM(F5:F6),"-")</f>
         <v>-</v>
       </c>
-      <c r="H14" s="12" t="str">
+      <c r="H14" s="13" t="str">
         <f aca="false">IFERROR(SUM(H5:H5)/SUM(G5:G5),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="12" t="str">
+      <c r="C15" s="13" t="str">
         <f aca="false">IFERROR(D14*D15,"-")</f>
         <v>-</v>
       </c>
-      <c r="D15" s="12" t="str">
+      <c r="D15" s="13" t="str">
         <f aca="false">IFERROR(E14*E15,"-")</f>
         <v>-</v>
       </c>
-      <c r="E15" s="12" t="str">
+      <c r="E15" s="13" t="str">
         <f aca="false">IFERROR(F14*F15,"-")</f>
         <v>-</v>
       </c>
-      <c r="F15" s="12" t="str">
+      <c r="F15" s="13" t="str">
         <f aca="false">IFERROR(G14*G15,"-")</f>
         <v>-</v>
       </c>
-      <c r="G15" s="12" t="str">
+      <c r="G15" s="13" t="str">
         <f aca="false">IFERROR(H14*H15,"-")</f>
         <v>-</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="14" t="n">
         <f aca="false">SUM(I5:I10)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="J17" s="14" t="n">
         <f aca="false">SUM(J5:J10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1153,67 +1218,339 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C12"/>
+  <dimension ref="B2:K16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
+      <c r="C4" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
+      <c r="B6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="5" t="n">
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <f aca="false">C7*$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!H5</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <f aca="false">'Loss Reserve Triangle'!H15</f>
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <f aca="false">IFERROR(1/F7,"-")</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <f aca="false">IFERROR(D7*(1-G7),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <f aca="false">IFERROR(E7+H7,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!I5</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <f aca="false">IFERROR(I7-J7,"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>0</v>
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <f aca="false">C8*$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!G6</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="18" t="str">
+        <f aca="false">'Loss Reserve Triangle'!G15</f>
+        <v>-</v>
+      </c>
+      <c r="G8" s="7" t="str">
+        <f aca="false">IFERROR(1/F8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H8" s="12" t="str">
+        <f aca="false">IFERROR(D8*(1-G8),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I8" s="14" t="str">
+        <f aca="false">IFERROR(E8+H8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J8" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!I6</f>
+        <v>-</v>
+      </c>
+      <c r="K8" s="12" t="str">
+        <f aca="false">IFERROR(I8-J8,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <f aca="false">C9*$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="str">
+        <f aca="false">'Loss Reserve Triangle'!F15</f>
+        <v>-</v>
+      </c>
+      <c r="G9" s="7" t="str">
+        <f aca="false">IFERROR(1/F9,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H9" s="12" t="str">
+        <f aca="false">IFERROR(D9*(1-G9),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I9" s="14" t="str">
+        <f aca="false">IFERROR(E9+H9,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J9" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!I7</f>
+        <v>-</v>
+      </c>
+      <c r="K9" s="12" t="str">
+        <f aca="false">IFERROR(I9-J9,"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <f aca="false">C5+C6-C7-C8</f>
-        <v>0</v>
+      <c r="B10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <f aca="false">C10*$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="str">
+        <f aca="false">'Loss Reserve Triangle'!E15</f>
+        <v>-</v>
+      </c>
+      <c r="G10" s="7" t="str">
+        <f aca="false">IFERROR(1/F10,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H10" s="12" t="str">
+        <f aca="false">IFERROR(D10*(1-G10),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I10" s="14" t="str">
+        <f aca="false">IFERROR(E10+H10,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J10" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!I8</f>
+        <v>-</v>
+      </c>
+      <c r="K10" s="12" t="str">
+        <f aca="false">IFERROR(I10-J10,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <f aca="false">C11*$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!D9</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="18" t="str">
+        <f aca="false">'Loss Reserve Triangle'!D15</f>
+        <v>-</v>
+      </c>
+      <c r="G11" s="7" t="str">
+        <f aca="false">IFERROR(1/F11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H11" s="12" t="str">
+        <f aca="false">IFERROR(D11*(1-G11),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I11" s="14" t="str">
+        <f aca="false">IFERROR(E11+H11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J11" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!I9</f>
+        <v>-</v>
+      </c>
+      <c r="K11" s="12" t="str">
+        <f aca="false">IFERROR(I11-J11,"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0</v>
+      <c r="B12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <f aca="false">C12*$C$4</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!C10</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="18" t="str">
+        <f aca="false">'Loss Reserve Triangle'!C15</f>
+        <v>-</v>
+      </c>
+      <c r="G12" s="7" t="str">
+        <f aca="false">IFERROR(1/F12,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H12" s="12" t="str">
+        <f aca="false">IFERROR(D12*(1-G12),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I12" s="14" t="str">
+        <f aca="false">IFERROR(E12+H12,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="J12" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!I10</f>
+        <v>-</v>
+      </c>
+      <c r="K12" s="12" t="str">
+        <f aca="false">IFERROR(I12-J12,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <f aca="false">SUM(C7:C12)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">SUM(D7:D12)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <f aca="false">SUM(H7:H12)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <f aca="false">SUM(I7:I12)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <f aca="false">SUM(J7:J12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1232,86 +1569,67 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D13"/>
+  <dimension ref="B2:C12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
-        <v>47</v>
+      <c r="B2" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="5" t="n">
+      <c r="B5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9" t="s">
-        <v>50</v>
+      <c r="B6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
-        <v>51</v>
+      <c r="B10" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C10" s="14" t="n">
-        <f aca="false">'Loss Reserve Triangle'!J17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <f aca="false">IFERROR(C5+C10,"-")</f>
+        <f aca="false">C5+C6-C7-C8</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="6" t="str">
-        <f aca="false">IFERROR(C10/C11,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="15" t="str">
-        <f aca="false">IFERROR(C11/C6,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>56</v>
+      <c r="B12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1330,74 +1648,86 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D12"/>
+  <dimension ref="B2:D13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>57</v>
+      <c r="B2" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
-        <v>47</v>
+      <c r="B4" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="5" t="n">
+      <c r="B5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="5" t="n">
+      <c r="B6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9" t="s">
-        <v>50</v>
+      <c r="B9" s="10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="14" t="str">
-        <f aca="false">IFERROR('Underwriting Ratios'!C5*(1-'Underwriting Ratios'!C12),"-")</f>
-        <v>-</v>
+      <c r="B10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!J17</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="13" t="str">
-        <f aca="false">IFERROR(C10+C5,"-")</f>
-        <v>-</v>
+      <c r="B11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <f aca="false">IFERROR(C5+C10,"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>62</v>
+      <c r="B12" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="C12" s="7" t="str">
+        <f aca="false">IFERROR(C10/C11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="19" t="str">
         <f aca="false">IFERROR(C11/C6,"-")</f>
         <v>-</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>63</v>
+      <c r="D13" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1416,107 +1746,193 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:D12"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="17" t="str">
+        <f aca="false">IFERROR('Underwriting Ratios'!C5*(1-'Underwriting Ratios'!C12),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="14" t="str">
+        <f aca="false">IFERROR(C10+C5,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f aca="false">IFERROR(C11/C6,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>64</v>
+      <c r="B2" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>69</v>
+      <c r="B4" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/18_Insurance_Actuarial/_template_INSURANCE.xlsx
+++ b/18_Insurance_Actuarial/_template_INSURANCE.xlsx
@@ -12,10 +12,13 @@
     <sheet name="Underwriting Ratios" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Loss Reserve Triangle" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Bornhuetter-Ferguson" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Embedded Value" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Reserve Summary" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Profitability" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="RefreshLog" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Mack Method" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Embedded Value" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Reserve Summary" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Profitability" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Sources" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Checks" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="RefreshLog" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="144">
   <si>
     <t xml:space="preserve">[INSURER] — Insurance / Actuarial Model</t>
   </si>
@@ -194,6 +197,81 @@
     <t xml:space="preserve">For the least mature year (highest CDF), chain-ladder leans hardest on the thinnest, noisiest actual data — that's exactly where BF's independent prior does the most work pulling the estimate away from a potentially unstable chain-ladder projection.</t>
   </si>
   <si>
+    <t xml:space="preserve">Mack Method — Chain-Ladder Standard Error / Reserve Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution-free: derives the reserve's standard error purely from how much each accident year's own development factor scattered around the volume-weighted average link factor -- no assumption about the underlying loss distribution, unlike a parametric bootstrap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link Factor Variance (sigma_k^2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev period k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link factor f_k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n (accident yrs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column sum S_k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma_k^2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev 1 -&gt; Dev 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev 2 -&gt; Dev 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev 3 -&gt; Dev 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev 4 -&gt; Dev 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev 5 -&gt; Dev 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n=1 gives zero degrees of freedom -- Mack's own recommended workaround, not a full estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed Triangle (chain-ladder-projected lower-right)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual data (green) where observed; projected (black) beyond the latest diagonal -- this is what feeds each accident year's future-period terms in the Mack formula below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per-Accident-Year Reserve Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserve (IBNR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mack MSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mack SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CV (SE/Reserve)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% Lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% Upper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total SE here is SQRT(sum of individual accident-year MSEs) -- it EXCLUDES the cross-accident-year covariance term Mack's full total-reserve formula includes (accident years share the same sigma_k^2 estimates, so their reserve errors are correlated, not independent). This therefore UNDERSTATES the true total reserve volatility -- a real reserve opinion needs the full covariance term, not this simplified sum-of-squares.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Embedded Value (life/health simplified)</t>
   </si>
   <si>
@@ -267,6 +345,105 @@
   </si>
   <si>
     <t xml:space="preserve">Why combined ratio alone can mislead: a carrier can run &gt;100% combined and still be profitable if investment income (float x yield) covers the gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each material assumption or convention in this model comes from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption / convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume-weighted chain-ladder link factors and CDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard actuarial loss-development methodology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses only accident years with data in both adjacent columns -- the denominator shrinks moving right through the triangle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bornhuetter-Ferguson blended reserving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bornhuetter &amp; Ferguson (1972)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer-reviewed methodology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires an independent a priori expected loss ratio (from pricing/plan), not derived from the same triangle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mack method standard error (distribution-free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mack, T. (1993), "Distribution-Free Calculation of the Standard Error of Chain Ladder Reserve Estimates"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total reserve SE reported here excludes the cross-accident-year covariance term Mack's full total-reserve formula includes -- understates true total volatility, documented directly on the sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mack's last-link-factor variance extrapolation (sigma_{n-1}^2 = MIN(...))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same Mack (1993) paper's own recommended workaround for the zero-degrees-of-freedom edge case at the thinnest development period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A necessary approximation, not a full estimate -- only 1 accident year contributes to the last link factor in a 6x6 triangle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live reconciliation identities -- independent of the model's own formulas, must tie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passes when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BF and chain-ladder converge exactly at full maturity (CDF=1, AY2020 -- the only row guaranteed fully developed in a 6-period triangle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) -- AY2020 has all 6 development periods, so CDF=1.000 exactly and the BF IBNR term vanishes, collapsing BF to the actual/chain-ladder figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mack reserve for the fully-developed accident year (AY2020) is exactly zero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) -- a fully-developed year has no future development periods, hence no reserve and no Mack SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed triangle's actual (upper-left) cells tie exactly to the source triangle (AY2020 full row + AY2021 actual portion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) -- confirms the green cross-sheet links, not stale hardcodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mack SE is non-negative for every accident year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE -- a standard error can never be negative by construction (it's a square root)</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -291,12 +468,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0\x"/>
+    <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="169" formatCode="#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.0\x"/>
+    <numFmt numFmtId="171" formatCode="General"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -448,7 +628,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -525,7 +705,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -850,6 +1050,218 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <f aca="false">IFERROR(IF(ISNUMBER('Bornhuetter-Ferguson'!K7),'Bornhuetter-Ferguson'!K7,0),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <f aca="false">'Mack Method'!D25</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <f aca="false">SUMPRODUCT(ABS('Mack Method'!C16:H16-'Loss Reserve Triangle'!C5:H5))+SUMPRODUCT(ABS('Mack Method'!C17:G17-'Loss Reserve Triangle'!C6:G6))</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="24" t="b">
+        <f aca="false">IF(COUNTIF('Mack Method'!F25:F30,"&lt;0")=0,TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:F14"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -1569,13 +1981,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C12"/>
+  <dimension ref="B2:I33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1583,53 +1995,585 @@
         <v>55</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0</v>
+      <c r="B5" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>0</v>
+      <c r="B6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="C7" s="13" t="str">
+        <f aca="false">'Loss Reserve Triangle'!$D$14</f>
+        <v>-</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <f aca="false">SUM('Loss Reserve Triangle'!$C$5:$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="20" t="str">
+        <f aca="false">IFERROR(SUMPRODUCT('Loss Reserve Triangle'!$C$5:$C$9,('Loss Reserve Triangle'!$D$5:$D$9/'Loss Reserve Triangle'!$C$5:$C$9-C7)^2)/(5-1),"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="C8" s="13" t="str">
+        <f aca="false">'Loss Reserve Triangle'!$E$14</f>
+        <v>-</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <f aca="false">SUM('Loss Reserve Triangle'!$D$5:$D$8)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="20" t="str">
+        <f aca="false">IFERROR(SUMPRODUCT('Loss Reserve Triangle'!$D$5:$D$8,('Loss Reserve Triangle'!$E$5:$E$8/'Loss Reserve Triangle'!$D$5:$D$8-C8)^2)/(4-1),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="13" t="str">
+        <f aca="false">'Loss Reserve Triangle'!$F$14</f>
+        <v>-</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <f aca="false">SUM('Loss Reserve Triangle'!$E$5:$E$7)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="20" t="str">
+        <f aca="false">IFERROR(SUMPRODUCT('Loss Reserve Triangle'!$E$5:$E$7,('Loss Reserve Triangle'!$F$5:$F$7/'Loss Reserve Triangle'!$E$5:$E$7-C9)^2)/(3-1),"-")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <f aca="false">C5+C6-C7-C8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>0</v>
+      <c r="B10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="13" t="str">
+        <f aca="false">'Loss Reserve Triangle'!$G$14</f>
+        <v>-</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <f aca="false">SUM('Loss Reserve Triangle'!$F$5:$F$6)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="20" t="str">
+        <f aca="false">IFERROR(SUMPRODUCT('Loss Reserve Triangle'!$F$5:$F$6,('Loss Reserve Triangle'!$G$5:$G$6/'Loss Reserve Triangle'!$F$5:$F$6-C10)^2)/(2-1),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="13" t="str">
+        <f aca="false">'Loss Reserve Triangle'!$H$14</f>
+        <v>-</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <f aca="false">SUM('Loss Reserve Triangle'!$G$5:$G$5)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="20" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(F10)),NOT(ISNUMBER(F9))),"-",MIN(F10,F9,F10^2/F9)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!C5</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!D5</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!E5</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!G5</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!H5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!D6</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!E6</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!F6</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!G6</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(G17)),NOT(ISNUMBER('Loss Reserve Triangle'!H$14))),"-",G17*'Loss Reserve Triangle'!H$14),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!C7</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!D7</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(F18)),NOT(ISNUMBER('Loss Reserve Triangle'!G$14))),"-",F18*'Loss Reserve Triangle'!G$14),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H18" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(G18)),NOT(ISNUMBER('Loss Reserve Triangle'!H$14))),"-",G18*'Loss Reserve Triangle'!H$14),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!C8</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!D8</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(E19)),NOT(ISNUMBER('Loss Reserve Triangle'!F$14))),"-",E19*'Loss Reserve Triangle'!F$14),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G19" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(F19)),NOT(ISNUMBER('Loss Reserve Triangle'!G$14))),"-",F19*'Loss Reserve Triangle'!G$14),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H19" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(G19)),NOT(ISNUMBER('Loss Reserve Triangle'!H$14))),"-",G19*'Loss Reserve Triangle'!H$14),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!D9</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(D20)),NOT(ISNUMBER('Loss Reserve Triangle'!E$14))),"-",D20*'Loss Reserve Triangle'!E$14),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F20" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(E20)),NOT(ISNUMBER('Loss Reserve Triangle'!F$14))),"-",E20*'Loss Reserve Triangle'!F$14),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G20" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(F20)),NOT(ISNUMBER('Loss Reserve Triangle'!G$14))),"-",F20*'Loss Reserve Triangle'!G$14),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H20" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(G20)),NOT(ISNUMBER('Loss Reserve Triangle'!H$14))),"-",G20*'Loss Reserve Triangle'!H$14),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(C21)),NOT(ISNUMBER('Loss Reserve Triangle'!D$14))),"-",C21*'Loss Reserve Triangle'!D$14),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E21" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(D21)),NOT(ISNUMBER('Loss Reserve Triangle'!E$14))),"-",D21*'Loss Reserve Triangle'!E$14),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F21" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(E21)),NOT(ISNUMBER('Loss Reserve Triangle'!F$14))),"-",E21*'Loss Reserve Triangle'!F$14),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G21" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(F21)),NOT(ISNUMBER('Loss Reserve Triangle'!G$14))),"-",F21*'Loss Reserve Triangle'!G$14),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H21" s="12" t="str">
+        <f aca="false">IFERROR(IF(OR(NOT(ISNUMBER(G21)),NOT(ISNUMBER('Loss Reserve Triangle'!H$14))),"-",G21*'Loss Reserve Triangle'!H$14),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!I5</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!J5</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <f aca="false">IFERROR(IF(ISNUMBER(E25),SQRT(E25),"-"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D25)),NOT(ISNUMBER(F25)),D25=0),"-",F25/D25)</f>
+        <v>-</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <f aca="false">IFERROR(D25-1.96*F25,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <f aca="false">IFERROR(D25+1.96*F25,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!I6</f>
+        <v>-</v>
+      </c>
+      <c r="D26" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!J6</f>
+        <v>-</v>
+      </c>
+      <c r="E26" s="20" t="str">
+        <f aca="false">IFERROR(('Loss Reserve Triangle'!I6)^2*(($F$11/$C$11^2)*(1/G17+1/$E$11)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F26" s="14" t="str">
+        <f aca="false">IFERROR(IF(ISNUMBER(E26),SQRT(E26),"-"),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G26" s="7" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D26)),NOT(ISNUMBER(F26)),D26=0),"-",F26/D26)</f>
+        <v>-</v>
+      </c>
+      <c r="H26" s="12" t="str">
+        <f aca="false">IFERROR(D26-1.96*F26,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I26" s="12" t="str">
+        <f aca="false">IFERROR(D26+1.96*F26,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!I7</f>
+        <v>-</v>
+      </c>
+      <c r="D27" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!J7</f>
+        <v>-</v>
+      </c>
+      <c r="E27" s="20" t="str">
+        <f aca="false">IFERROR(('Loss Reserve Triangle'!I7)^2*(($F$10/$C$10^2)*(1/F18+1/$E$10)+($F$11/$C$11^2)*(1/G18+1/$E$11)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F27" s="14" t="str">
+        <f aca="false">IFERROR(IF(ISNUMBER(E27),SQRT(E27),"-"),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G27" s="7" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D27)),NOT(ISNUMBER(F27)),D27=0),"-",F27/D27)</f>
+        <v>-</v>
+      </c>
+      <c r="H27" s="12" t="str">
+        <f aca="false">IFERROR(D27-1.96*F27,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I27" s="12" t="str">
+        <f aca="false">IFERROR(D27+1.96*F27,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!I8</f>
+        <v>-</v>
+      </c>
+      <c r="D28" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!J8</f>
+        <v>-</v>
+      </c>
+      <c r="E28" s="20" t="str">
+        <f aca="false">IFERROR(('Loss Reserve Triangle'!I8)^2*(($F$9/$C$9^2)*(1/E19+1/$E$9)+($F$10/$C$10^2)*(1/F19+1/$E$10)+($F$11/$C$11^2)*(1/G19+1/$E$11)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F28" s="14" t="str">
+        <f aca="false">IFERROR(IF(ISNUMBER(E28),SQRT(E28),"-"),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G28" s="7" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D28)),NOT(ISNUMBER(F28)),D28=0),"-",F28/D28)</f>
+        <v>-</v>
+      </c>
+      <c r="H28" s="12" t="str">
+        <f aca="false">IFERROR(D28-1.96*F28,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I28" s="12" t="str">
+        <f aca="false">IFERROR(D28+1.96*F28,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!I9</f>
+        <v>-</v>
+      </c>
+      <c r="D29" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!J9</f>
+        <v>-</v>
+      </c>
+      <c r="E29" s="20" t="str">
+        <f aca="false">IFERROR(('Loss Reserve Triangle'!I9)^2*(($F$8/$C$8^2)*(1/D20+1/$E$8)+($F$9/$C$9^2)*(1/E20+1/$E$9)+($F$10/$C$10^2)*(1/F20+1/$E$10)+($F$11/$C$11^2)*(1/G20+1/$E$11)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F29" s="14" t="str">
+        <f aca="false">IFERROR(IF(ISNUMBER(E29),SQRT(E29),"-"),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G29" s="7" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D29)),NOT(ISNUMBER(F29)),D29=0),"-",F29/D29)</f>
+        <v>-</v>
+      </c>
+      <c r="H29" s="12" t="str">
+        <f aca="false">IFERROR(D29-1.96*F29,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I29" s="12" t="str">
+        <f aca="false">IFERROR(D29+1.96*F29,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!I10</f>
+        <v>-</v>
+      </c>
+      <c r="D30" s="17" t="str">
+        <f aca="false">'Loss Reserve Triangle'!J10</f>
+        <v>-</v>
+      </c>
+      <c r="E30" s="20" t="str">
+        <f aca="false">IFERROR(('Loss Reserve Triangle'!I10)^2*(($F$7/$C$7^2)*(1/C21+1/$E$7)+($F$8/$C$8^2)*(1/D21+1/$E$8)+($F$9/$C$9^2)*(1/E21+1/$E$9)+($F$10/$C$10^2)*(1/F21+1/$E$10)+($F$11/$C$11^2)*(1/G21+1/$E$11)),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F30" s="14" t="str">
+        <f aca="false">IFERROR(IF(ISNUMBER(E30),SQRT(E30),"-"),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G30" s="7" t="str">
+        <f aca="false">IF(OR(NOT(ISNUMBER(D30)),NOT(ISNUMBER(F30)),D30=0),"-",F30/D30)</f>
+        <v>-</v>
+      </c>
+      <c r="H30" s="12" t="str">
+        <f aca="false">IFERROR(D30-1.96*F30,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I30" s="12" t="str">
+        <f aca="false">IFERROR(D30+1.96*F30,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <f aca="false">IFERROR(SUM(D25:D30),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <f aca="false">IFERROR(SQRT(SUM(E25:E30)),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1648,28 +2592,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D13"/>
+  <dimension ref="B2:C12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -1677,57 +2616,43 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10" t="s">
-        <v>66</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <f aca="false">'Loss Reserve Triangle'!J17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <f aca="false">IFERROR(C5+C10,"-")</f>
+        <v>85</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <f aca="false">C5+C6-C7-C8</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="7" t="str">
-        <f aca="false">IFERROR(C10/C11,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="19" t="str">
-        <f aca="false">IFERROR(C11/C6,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>72</v>
+        <v>86</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1746,28 +2671,28 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D12"/>
+  <dimension ref="B2:D13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="10" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -1775,7 +2700,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
@@ -1783,37 +2708,49 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="17" t="str">
-        <f aca="false">IFERROR('Underwriting Ratios'!C5*(1-'Underwriting Ratios'!C12),"-")</f>
-        <v>-</v>
+        <v>92</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <f aca="false">'Loss Reserve Triangle'!J17</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="14" t="str">
-        <f aca="false">IFERROR(C10+C5,"-")</f>
-        <v>-</v>
+        <v>93</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <f aca="false">IFERROR(C5+C10,"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="8" t="str">
+        <v>94</v>
+      </c>
+      <c r="C12" s="7" t="str">
+        <f aca="false">IFERROR(C10/C11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="21" t="str">
         <f aca="false">IFERROR(C11/C6,"-")</f>
         <v>-</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>79</v>
+      <c r="D13" s="9" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1832,107 +2769,181 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F14"/>
+  <dimension ref="B2:D12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>85</v>
+      <c r="B4" s="10" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
+      <c r="B5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
+      <c r="B6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="17" t="str">
+        <f aca="false">IFERROR('Underwriting Ratios'!C5*(1-'Underwriting Ratios'!C12),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="14" t="str">
+        <f aca="false">IFERROR(C10+C5,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="8" t="str">
+        <f aca="false">IFERROR(C11/C6,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
+      <c r="B7" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
+      <c r="B8" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="B9" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>124</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
